--- a/reports/2026-03-14.xlsx
+++ b/reports/2026-03-14.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-14 06:45 UTC</t>
+          <t>2026-03-14 10:15 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-14_1773470654209</t>
+          <t>2026-03-14_1773483267911</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GRTUSDT</t>
+          <t>TRUMPUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Graph</t>
+          <t>OFFICIAL TRUMP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>ENTER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -930,84 +930,80 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63.968</v>
+        <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>79.95999999999999</v>
+        <v>70</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02640959622869432</v>
+        <v>3.273047884957256</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02638</v>
+        <v>3.923</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1120661915389953</v>
+        <v>19.85770260282127</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.02261</v>
+        <v>3.035</v>
       </c>
       <c r="T2" t="n">
-        <v>14.38718031048888</v>
+        <v>7.27297287801107</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03020919245738865</v>
+        <v>3.511095769914513</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03400878868608297</v>
+        <v>3.749143654871769</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0378083849147773</v>
+        <v>3.987191539829025</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03791469194312642</v>
+        <v>0.02547446185200188</v>
       </c>
       <c r="AA2" t="n">
-        <v>22533.0120156</v>
+        <v>164183.42539</v>
       </c>
       <c r="AB2" t="n">
-        <v>12251.9781237</v>
+        <v>170707.86868</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.498956</v>
+        <v>4.678425</v>
       </c>
       <c r="AD2" t="n">
-        <v>254.069237</v>
+        <v>7.837018</v>
       </c>
       <c r="AE2" t="n">
-        <v>237286526.8349056</v>
+        <v>914794088.206045</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1022,12 +1018,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TURBOUSDT</t>
+          <t>GRTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>The Graph</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1037,7 +1033,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1051,10 +1047,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62.392</v>
+        <v>63.968</v>
       </c>
       <c r="I3" t="n">
-        <v>77.98999999999999</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -1078,57 +1074,57 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001010902989841661</v>
+        <v>0.02640959622869432</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001141</v>
+        <v>0.02627</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.86938622851592</v>
+        <v>-0.5285814576091452</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.000876</v>
+        <v>0.02261</v>
       </c>
       <c r="T3" t="n">
-        <v>13.34480075707278</v>
+        <v>14.38718031048888</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001145805979683323</v>
+        <v>0.03020919245738865</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001280708969524984</v>
+        <v>0.03400878868608297</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001415611959366646</v>
+        <v>0.0378083849147773</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.192796424502668</v>
+        <v>0.03807348181992409</v>
       </c>
       <c r="AA3" t="n">
-        <v>9881.433054928</v>
+        <v>18322.4211032</v>
       </c>
       <c r="AB3" t="n">
-        <v>8495.584516289</v>
+        <v>12639.2128192</v>
       </c>
       <c r="AC3" t="n">
-        <v>37.834685</v>
+        <v>19.306984</v>
       </c>
       <c r="AD3" t="n">
-        <v>369.950816</v>
+        <v>268.701897</v>
       </c>
       <c r="AE3" t="n">
-        <v>79003732.82059467</v>
+        <v>247839478.1186036</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1143,12 +1139,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALGOUSDT</t>
+          <t>TURBOUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Turbo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>62.184</v>
+        <v>62.392</v>
       </c>
       <c r="I4" t="n">
-        <v>77.73</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1187,25 +1183,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0881281822103617</v>
+        <v>0.001010902989841661</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09217</v>
+        <v>0.0010654</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.58629429118429</v>
+        <v>5.390923828098915</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1213,19 +1209,19 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.0806</v>
+        <v>0.000876</v>
       </c>
       <c r="T4" t="n">
-        <v>8.542309646637152</v>
+        <v>13.34480075707278</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09565636442072339</v>
+        <v>0.001145805979683323</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1031845466310851</v>
+        <v>0.001280708969524984</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1107127288414468</v>
+        <v>0.001415611959366646</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1234,22 +1230,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1086130118388063</v>
+        <v>0.1220027215991822</v>
       </c>
       <c r="AA4" t="n">
-        <v>58469.0676636</v>
+        <v>13261.894231097</v>
       </c>
       <c r="AB4" t="n">
-        <v>54732.5031165</v>
+        <v>10692.633935367</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.451381</v>
+        <v>32.077029</v>
       </c>
       <c r="AD4" t="n">
-        <v>30.931245</v>
+        <v>239.3828</v>
       </c>
       <c r="AE4" t="n">
-        <v>821498659.5548553</v>
+        <v>73545218.39797568</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1264,12 +1260,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>ALGOUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1279,50 +1275,54 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>61.2</v>
+        <v>62.184</v>
       </c>
       <c r="I5" t="n">
-        <v>68</v>
+        <v>77.73</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008539124282940763</v>
+        <v>0.0881281822103617</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01074</v>
+        <v>0.09132999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.774021364885</v>
+        <v>3.633137220504068</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.007486231252880395</v>
+        <v>0.0806</v>
       </c>
       <c r="T5" t="n">
-        <v>12.33022257520962</v>
+        <v>8.542309646637152</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009592017313001132</v>
+        <v>0.09565636442072339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0106449103430615</v>
+        <v>0.1031845466310851</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01169780337312187</v>
+        <v>0.1107127288414468</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1351,22 +1351,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03074443455860293</v>
+        <v>0.09852756034812288</v>
       </c>
       <c r="AA5" t="n">
-        <v>9597.195318724</v>
+        <v>109303.3702501</v>
       </c>
       <c r="AB5" t="n">
-        <v>17536.443041871</v>
+        <v>96946.0068477</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.126211</v>
+        <v>7.98636</v>
       </c>
       <c r="AD5" t="n">
-        <v>82.92800800000001</v>
+        <v>16.734708</v>
       </c>
       <c r="AE5" t="n">
-        <v>107477184.4761735</v>
+        <v>812687003.9166681</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1433,13 +1433,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>18.16763992150123</v>
+        <v>18.5016932800241</v>
       </c>
       <c r="P6" t="n">
-        <v>21.814</v>
+        <v>22.2385</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.07063159691609</v>
+        <v>20.19710662921026</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>16.49196841873954</v>
+        <v>16.69515717614323</v>
       </c>
       <c r="T6" t="n">
-        <v>9.223385701180424</v>
+        <v>9.764166320016539</v>
       </c>
       <c r="U6" t="n">
-        <v>19.84331142426293</v>
+        <v>20.30822938390498</v>
       </c>
       <c r="V6" t="n">
-        <v>21.51898292702462</v>
+        <v>22.11476548778586</v>
       </c>
       <c r="W6" t="n">
-        <v>23.19465442978631</v>
+        <v>23.92130159166673</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1468,22 +1468,22 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1452886923098024</v>
+        <v>0.0004496696052724645</v>
       </c>
       <c r="AA6" t="n">
-        <v>12996.092697</v>
+        <v>13416.161101</v>
       </c>
       <c r="AB6" t="n">
-        <v>9155.83409</v>
+        <v>10316.136733</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.281283</v>
+        <v>29.541366</v>
       </c>
       <c r="AD6" t="n">
-        <v>107.994066</v>
+        <v>96.152759</v>
       </c>
       <c r="AE6" t="n">
-        <v>425424556.8357913</v>
+        <v>434502754.9490408</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TAOUSDT</t>
+          <t>MELANIAUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Official Melania Meme</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>61.2</v>
+        <v>60.344</v>
       </c>
       <c r="I7" t="n">
-        <v>68</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1538,25 +1538,25 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>219.1247632833021</v>
+        <v>0.1112803252979652</v>
       </c>
       <c r="P7" t="n">
-        <v>237.53</v>
+        <v>0.11982</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.39943256112139</v>
+        <v>7.674020253956781</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>204.2569217840868</v>
+        <v>0.10264</v>
       </c>
       <c r="T7" t="n">
-        <v>6.78510327926425</v>
+        <v>7.764468044849582</v>
       </c>
       <c r="U7" t="n">
-        <v>233.9926047825175</v>
+        <v>0.1199206505959303</v>
       </c>
       <c r="V7" t="n">
-        <v>248.8604462817329</v>
+        <v>0.1285609758938955</v>
       </c>
       <c r="W7" t="n">
-        <v>263.7282877809482</v>
+        <v>0.1372013011918607</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -1585,29 +1585,33 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05898462186643622</v>
+        <v>0.4835751208937779</v>
       </c>
       <c r="AA7" t="n">
-        <v>226657.46683</v>
+        <v>3415.4931188</v>
       </c>
       <c r="AB7" t="n">
-        <v>203045.18005</v>
+        <v>4401.2964646</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.694521</v>
+        <v>78.270025</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.198316</v>
+        <v>2315.714486</v>
       </c>
       <c r="AE7" t="n">
-        <v>2551194347.267691</v>
+        <v>119887969.8846735</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1615,12 +1619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MELANIAUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Official Melania Meme</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1630,24 +1634,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60.344</v>
+        <v>58.32</v>
       </c>
       <c r="I8" t="n">
-        <v>75.43000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1655,25 +1659,25 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1112803252979652</v>
+        <v>220.6024049341364</v>
       </c>
       <c r="P8" t="n">
-        <v>0.12347</v>
+        <v>235.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.95402504386616</v>
+        <v>6.916332154411009</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1681,19 +1685,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.10264</v>
+        <v>205.4514637276878</v>
       </c>
       <c r="T8" t="n">
-        <v>7.764468044849582</v>
+        <v>6.867985510390086</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1199206505959303</v>
+        <v>235.7533461405849</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1285609758938955</v>
+        <v>250.9042873470335</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1372013011918607</v>
+        <v>266.055228553482</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1702,33 +1706,29 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3883180972413302</v>
+        <v>0.03814286622449341</v>
       </c>
       <c r="AA8" t="n">
-        <v>2868.5310179</v>
+        <v>341577.48471</v>
       </c>
       <c r="AB8" t="n">
-        <v>4581.8561025</v>
+        <v>218731.28955</v>
       </c>
       <c r="AC8" t="n">
-        <v>65.49919800000001</v>
+        <v>4.779214</v>
       </c>
       <c r="AD8" t="n">
-        <v>2669.233357</v>
+        <v>6.364134</v>
       </c>
       <c r="AE8" t="n">
-        <v>123955104.8551496</v>
+        <v>2541602397.988404</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1736,39 +1736,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEEPUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DeepBook Protocol</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>73.752</v>
+        <v>55.44</v>
       </c>
       <c r="I9" t="n">
-        <v>92.19</v>
+        <v>61.6</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02956494343623838</v>
+        <v>0.008738855304062911</v>
       </c>
       <c r="P9" t="n">
-        <v>0.033455</v>
+        <v>0.0107432</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.15766618039085</v>
+        <v>22.93600965111779</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1802,43 +1802,43 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.021229</v>
+        <v>0.007609798769052171</v>
       </c>
       <c r="T9" t="n">
-        <v>28.19536406087229</v>
+        <v>12.91995914483002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03790088687247675</v>
+        <v>0.009867911839073651</v>
       </c>
       <c r="V9" t="n">
-        <v>0.04623683030871513</v>
+        <v>0.01099696837408439</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05457277374495351</v>
+        <v>0.01212602490909513</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9999999999999996</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.06278308444324912</v>
+        <v>0.03259922972677217</v>
       </c>
       <c r="AA9" t="n">
-        <v>23243.96057886</v>
+        <v>8507.247731256</v>
       </c>
       <c r="AB9" t="n">
-        <v>22980.18209754</v>
+        <v>7925.514306041</v>
       </c>
       <c r="AC9" t="n">
-        <v>33.232862</v>
+        <v>27.004767</v>
       </c>
       <c r="AD9" t="n">
-        <v>56.92672</v>
+        <v>93.960216</v>
       </c>
       <c r="AE9" t="n">
-        <v>164765109.4499469</v>
+        <v>107747011.2370479</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         <v>0.1595329806088012</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1789</v>
+        <v>0.1764</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.13982169535821</v>
+        <v>10.57274760794402</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1940,22 +1940,22 @@
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0559127760693412</v>
+        <v>0.05667327854915782</v>
       </c>
       <c r="AA10" t="n">
-        <v>96223.940884</v>
+        <v>121343.175687</v>
       </c>
       <c r="AB10" t="n">
-        <v>69073.163436</v>
+        <v>78684.82238100001</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.144919</v>
+        <v>2.833664</v>
       </c>
       <c r="AD10" t="n">
-        <v>11.800884</v>
+        <v>10.121816</v>
       </c>
       <c r="AE10" t="n">
-        <v>404691116.8727577</v>
+        <v>399606786.6116833</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         <v>0.05096304562042638</v>
       </c>
       <c r="P11" t="n">
-        <v>0.05483</v>
+        <v>0.05481</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.587761548583183</v>
+        <v>7.548517426187207</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2057,22 +2057,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01823985408116028</v>
+        <v>0.03648303538854285</v>
       </c>
       <c r="AA11" t="n">
-        <v>30093.2504305</v>
+        <v>37315.7105057</v>
       </c>
       <c r="AB11" t="n">
-        <v>19921.0638961</v>
+        <v>21714.619116</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.505438</v>
+        <v>9.135313</v>
       </c>
       <c r="AD11" t="n">
-        <v>43.343586</v>
+        <v>37.681755</v>
       </c>
       <c r="AE11" t="n">
-        <v>284758656.214079</v>
+        <v>285063000.5771754</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BERAUSDT</t>
+          <t>RSRUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Berachain</t>
+          <t>Reserve Rights</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2116,15 +2116,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>66.944</v>
+        <v>66.512</v>
       </c>
       <c r="I12" t="n">
-        <v>83.68000000000001</v>
+        <v>83.14</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>none</t>
@@ -2139,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5830684568323188</v>
+        <v>0.00160169917178106</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6249</v>
+        <v>0.001749</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.174379385045571</v>
+        <v>9.196535205493328</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2153,19 +2157,19 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.3345</v>
+        <v>0.001341</v>
       </c>
       <c r="T12" t="n">
-        <v>42.63109312802409</v>
+        <v>16.27641297280357</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8316369136646375</v>
+        <v>0.001862398343562119</v>
       </c>
       <c r="V12" t="n">
-        <v>1.080205370496956</v>
+        <v>0.002123097515343179</v>
       </c>
       <c r="W12" t="n">
-        <v>1.328773827329275</v>
+        <v>0.002383796687124239</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2174,22 +2178,22 @@
         <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06397952655149648</v>
+        <v>0.05712653527563073</v>
       </c>
       <c r="AA12" t="n">
-        <v>4859.12838</v>
+        <v>8456.18105612</v>
       </c>
       <c r="AB12" t="n">
-        <v>6306.343639</v>
+        <v>9615.20476339</v>
       </c>
       <c r="AC12" t="n">
-        <v>39.151452</v>
+        <v>38.947403</v>
       </c>
       <c r="AD12" t="n">
-        <v>127.289717</v>
+        <v>221.605277</v>
       </c>
       <c r="AE12" t="n">
-        <v>143080254.7114663</v>
+        <v>109321788.5084283</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2204,12 +2208,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MOODENGUSDT</t>
+          <t>MEWUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Moo Deng (moodengsol.com)</t>
+          <t>cat in a dogs world</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2233,10 +2237,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>66.08799999999999</v>
+        <v>66.488</v>
       </c>
       <c r="I13" t="n">
-        <v>82.61</v>
+        <v>83.11</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -2260,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05069032494417323</v>
+        <v>0.0006117059688524329</v>
       </c>
       <c r="P13" t="n">
-        <v>0.05351</v>
+        <v>0.0006357</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.562550760785534</v>
+        <v>3.922477851994843</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2274,43 +2278,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.038</v>
+        <v>0.0004931</v>
       </c>
       <c r="T13" t="n">
-        <v>25.03500413175388</v>
+        <v>19.38937576086416</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06338064988834646</v>
+        <v>0.0007303119377048658</v>
       </c>
       <c r="V13" t="n">
-        <v>0.07607097483251971</v>
+        <v>0.0008489179065572987</v>
       </c>
       <c r="W13" t="n">
-        <v>0.08876129977669295</v>
+        <v>0.0009675238754097315</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.09344921035417519</v>
+        <v>0.1572821642025833</v>
       </c>
       <c r="AA13" t="n">
-        <v>11526.3521805</v>
+        <v>2124.815830654</v>
       </c>
       <c r="AB13" t="n">
-        <v>7202.9094664</v>
+        <v>2620.960484824</v>
       </c>
       <c r="AC13" t="n">
-        <v>27.742796</v>
+        <v>5833.535506</v>
       </c>
       <c r="AD13" t="n">
-        <v>3294.336159</v>
+        <v>25567.534447</v>
       </c>
       <c r="AE13" t="n">
-        <v>53112472.07965237</v>
+        <v>56664633.60854564</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2325,12 +2329,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BBUSDT</t>
+          <t>MOODENGUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BounceBit</t>
+          <t>Moo Deng (moodengsol.com)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2340,7 +2344,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2354,10 +2358,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>65.93600000000001</v>
+        <v>66.08799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>82.42</v>
+        <v>82.61</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2381,57 +2385,57 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02786894629479462</v>
+        <v>0.05069032494417323</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02767</v>
+        <v>0.05315</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.7138637130022385</v>
+        <v>4.85235606308636</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.0235</v>
+        <v>0.038</v>
       </c>
       <c r="T14" t="n">
-        <v>15.67675450869363</v>
+        <v>25.03500413175388</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03223789258958924</v>
+        <v>0.06338064988834646</v>
       </c>
       <c r="V14" t="n">
-        <v>0.03660683888438386</v>
+        <v>0.07607097483251971</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04097578517917849</v>
+        <v>0.08876129977669295</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1084402674859887</v>
+        <v>0.09401146939926941</v>
       </c>
       <c r="AA14" t="n">
-        <v>6602.2553133</v>
+        <v>12655.1693195</v>
       </c>
       <c r="AB14" t="n">
-        <v>1255.2760289</v>
+        <v>6873.4900956</v>
       </c>
       <c r="AC14" t="n">
-        <v>127.73085</v>
+        <v>28.029084</v>
       </c>
       <c r="AD14" t="n">
-        <v>221.811781</v>
+        <v>3562.053653</v>
       </c>
       <c r="AE14" t="n">
-        <v>28889644.70188995</v>
+        <v>52669104.87262756</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HUMAUSDT</t>
+          <t>BBUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Huma Finance</t>
+          <t>BounceBit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2461,7 +2465,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2475,15 +2479,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>63.52</v>
+        <v>65.93600000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>79.40000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>none</t>
@@ -2498,57 +2506,57 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01575536570152586</v>
+        <v>0.02786894629479462</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01753</v>
+        <v>0.02754</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.26368205025079</v>
+        <v>-1.180332730613731</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.01102</v>
+        <v>0.0235</v>
       </c>
       <c r="T15" t="n">
-        <v>30.05557466093761</v>
+        <v>15.67675450869363</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02049073140305172</v>
+        <v>0.03223789258958924</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02522609710457759</v>
+        <v>0.03660683888438386</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02996146280610345</v>
+        <v>0.04097578517917849</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0570613409415098</v>
+        <v>0.1815211472136556</v>
       </c>
       <c r="AA15" t="n">
-        <v>5229.3499519</v>
+        <v>3412.7974754</v>
       </c>
       <c r="AB15" t="n">
-        <v>12676.771829</v>
+        <v>646.6380369</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.238501</v>
+        <v>123.938431</v>
       </c>
       <c r="AD15" t="n">
-        <v>96.207116</v>
+        <v>186.237008</v>
       </c>
       <c r="AE15" t="n">
-        <v>51062035.87446485</v>
+        <v>28835227.77215733</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2563,12 +2571,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RESOLVUSDT</t>
+          <t>HUMAUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Resolv</t>
+          <t>Huma Finance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2578,33 +2586,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_too_early</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>61.2</v>
+        <v>63.52</v>
       </c>
       <c r="I16" t="n">
-        <v>68</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>rebound_not_confirmed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>none</t>
@@ -2619,57 +2623,57 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09645174982689825</v>
+        <v>0.01575536570152586</v>
       </c>
       <c r="P16" t="n">
-        <v>0.07854999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="Q16" t="n">
-        <v>-18.56031628148425</v>
+        <v>9.169157516503912</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.09490090622717488</v>
+        <v>0.01102</v>
       </c>
       <c r="T16" t="n">
-        <v>1.607895763951053</v>
+        <v>30.05557466093761</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09800259342662161</v>
+        <v>0.02049073140305172</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09955343702634498</v>
+        <v>0.02522609710457759</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1011042806260683</v>
+        <v>0.02996146280610345</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="Y16" t="n">
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1274534794799934</v>
+        <v>0.05815644082581908</v>
       </c>
       <c r="AA16" t="n">
-        <v>18792.5830865</v>
+        <v>9541.837968400001</v>
       </c>
       <c r="AB16" t="n">
-        <v>16851.7567472</v>
+        <v>8800.561651800001</v>
       </c>
       <c r="AC16" t="n">
-        <v>35.63184</v>
+        <v>29.970831</v>
       </c>
       <c r="AD16" t="n">
-        <v>65.257327</v>
+        <v>123.826843</v>
       </c>
       <c r="AE16" t="n">
-        <v>29111845.02402832</v>
+        <v>49876969.64514145</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2684,12 +2688,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RSRUSDT</t>
+          <t>NAORISUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reserve Rights</t>
+          <t>Naoris Protocol</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2699,33 +2703,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60.008</v>
+        <v>61.2</v>
       </c>
       <c r="I17" t="n">
-        <v>75.01000000000001</v>
+        <v>68</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>none</t>
@@ -2740,13 +2740,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00160169917178106</v>
+        <v>0.06254009925707937</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001756</v>
+        <v>0.07283000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.633571081101366</v>
+        <v>16.4532849566206</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2754,43 +2754,43 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.001341</v>
+        <v>0.05247160377082919</v>
       </c>
       <c r="T17" t="n">
-        <v>16.27641297280357</v>
+        <v>16.09926368178966</v>
       </c>
       <c r="U17" t="n">
-        <v>0.001862398343562119</v>
+        <v>0.07260859474332956</v>
       </c>
       <c r="V17" t="n">
-        <v>0.002123097515343179</v>
+        <v>0.08267709022957974</v>
       </c>
       <c r="W17" t="n">
-        <v>0.002383796687124239</v>
+        <v>0.09274558571582991</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y17" t="n">
         <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.05683432793407973</v>
+        <v>0.2195992314027002</v>
       </c>
       <c r="AA17" t="n">
-        <v>9891.07759083</v>
+        <v>6329.3175794</v>
       </c>
       <c r="AB17" t="n">
-        <v>12581.41283404</v>
+        <v>7010.293770400001</v>
       </c>
       <c r="AC17" t="n">
-        <v>34.171257</v>
+        <v>28.065496</v>
       </c>
       <c r="AD17" t="n">
-        <v>109.38859</v>
+        <v>508.449304</v>
       </c>
       <c r="AE17" t="n">
-        <v>109789465.2251928</v>
+        <v>43521596.65752868</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>RESOLVUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Resolv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2820,70 +2820,74 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_too_early</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>58.736</v>
+        <v>61.2</v>
       </c>
       <c r="I18" t="n">
-        <v>73.42</v>
+        <v>68</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>rebound_not_confirmed</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5306211633169757</v>
+        <v>0.09475539271366505</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5471</v>
+        <v>0.07512000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.105574715492532</v>
+        <v>-20.72219021137923</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.3792</v>
+        <v>0.09426273288366489</v>
       </c>
       <c r="T18" t="n">
-        <v>28.53658575742138</v>
+        <v>0.5199280124234131</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6820423266339515</v>
+        <v>0.09524805254366521</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8334634899509272</v>
+        <v>0.09574071237366537</v>
       </c>
       <c r="W18" t="n">
-        <v>0.984884653267903</v>
+        <v>0.09623337220366553</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -2892,22 +2896,22 @@
         <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.05481955230698345</v>
+        <v>0.1598508059144918</v>
       </c>
       <c r="AA18" t="n">
-        <v>152420.669825</v>
+        <v>17899.0061987</v>
       </c>
       <c r="AB18" t="n">
-        <v>192009.143558</v>
+        <v>17117.0463683</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.444725</v>
+        <v>27.590674</v>
       </c>
       <c r="AD18" t="n">
-        <v>21.968995</v>
+        <v>55.893121</v>
       </c>
       <c r="AE18" t="n">
-        <v>407073036.653609</v>
+        <v>27934006.22107466</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2922,12 +2926,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JSTUSDT</t>
+          <t>DEEPUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>DeepBook Protocol</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2942,19 +2946,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>58.32</v>
+        <v>59.448</v>
       </c>
       <c r="I19" t="n">
-        <v>64.8</v>
+        <v>74.31</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2974,13 +2978,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.05283073888656207</v>
+        <v>0.02956494343623838</v>
       </c>
       <c r="P19" t="n">
-        <v>0.05559</v>
+        <v>0.033675</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.222832713664305</v>
+        <v>13.90179072260234</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2988,43 +2992,43 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.05121085551843595</v>
+        <v>0.021229</v>
       </c>
       <c r="T19" t="n">
-        <v>3.066175870839743</v>
+        <v>28.19536406087229</v>
       </c>
       <c r="U19" t="n">
-        <v>0.05445062225468818</v>
+        <v>0.03790088687247675</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0560705056228143</v>
+        <v>0.04623683030871513</v>
       </c>
       <c r="W19" t="n">
-        <v>0.05769038899094042</v>
+        <v>0.05457277374495351</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="Y19" t="n">
         <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.05401026194976201</v>
+        <v>0.01780626780626502</v>
       </c>
       <c r="AA19" t="n">
-        <v>4254.1169366</v>
+        <v>17106.27211429</v>
       </c>
       <c r="AB19" t="n">
-        <v>2820.683811</v>
+        <v>24102.90714516</v>
       </c>
       <c r="AC19" t="n">
-        <v>67.95941000000001</v>
+        <v>27.66747</v>
       </c>
       <c r="AD19" t="n">
-        <v>2998.790419</v>
+        <v>48.12784</v>
       </c>
       <c r="AE19" t="n">
-        <v>490006042.6826856</v>
+        <v>165609749.4710273</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3039,12 +3043,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAORISUSDT</t>
+          <t>BERAUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Naoris Protocol</t>
+          <t>Berachain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3059,19 +3063,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>58.32</v>
+        <v>56.848</v>
       </c>
       <c r="I20" t="n">
-        <v>64.8</v>
+        <v>71.06</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -3091,13 +3095,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06137695176902147</v>
+        <v>0.5830684568323188</v>
       </c>
       <c r="P20" t="n">
-        <v>0.07275</v>
+        <v>0.6367</v>
       </c>
       <c r="Q20" t="n">
-        <v>18.52983555419707</v>
+        <v>9.198155472009152</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3105,43 +3109,43 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.05160960220824248</v>
+        <v>0.3345</v>
       </c>
       <c r="T20" t="n">
-        <v>15.91370910294836</v>
+        <v>42.63109312802409</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07114430132980046</v>
+        <v>0.8316369136646375</v>
       </c>
       <c r="V20" t="n">
-        <v>0.08091165089057946</v>
+        <v>1.080205370496956</v>
       </c>
       <c r="W20" t="n">
-        <v>0.09067900045135846</v>
+        <v>1.328773827329275</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.2759001241550638</v>
+        <v>0.09420631182288175</v>
       </c>
       <c r="AA20" t="n">
-        <v>7380.564213199999</v>
+        <v>3751.881669</v>
       </c>
       <c r="AB20" t="n">
-        <v>6734.0402046</v>
+        <v>6738.777401</v>
       </c>
       <c r="AC20" t="n">
-        <v>39.388101</v>
+        <v>37.594548</v>
       </c>
       <c r="AD20" t="n">
-        <v>566.595345</v>
+        <v>129.770871</v>
       </c>
       <c r="AE20" t="n">
-        <v>43297744.72711914</v>
+        <v>145939706.3192202</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3156,12 +3160,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CYBERUSDT</t>
+          <t>JSTUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3171,33 +3175,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>57.464</v>
+        <v>55.44</v>
       </c>
       <c r="I21" t="n">
-        <v>71.83</v>
+        <v>61.6</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>none</t>
@@ -3212,33 +3212,33 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5488674060370984</v>
+        <v>0.05304114470958664</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5645</v>
+        <v>0.05531</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.848154907898648</v>
+        <v>4.277538320177476</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0.4252</v>
+        <v>0.05136088983654279</v>
       </c>
       <c r="T21" t="n">
-        <v>22.5313809267697</v>
+        <v>3.16783297616156</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6725348120741967</v>
+        <v>0.0547213995826305</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7962022181112951</v>
+        <v>0.05640165445567436</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9198696241483935</v>
+        <v>0.05808190932871822</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -3247,22 +3247,22 @@
         <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1240365021706448</v>
+        <v>0.05423483684352401</v>
       </c>
       <c r="AA21" t="n">
-        <v>16996.499024</v>
+        <v>7440.8248442</v>
       </c>
       <c r="AB21" t="n">
-        <v>1094.503648</v>
+        <v>2066.8785401</v>
       </c>
       <c r="AC21" t="n">
-        <v>92.717097</v>
+        <v>81.15847100000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>291.077853</v>
+        <v>2922.945883</v>
       </c>
       <c r="AE21" t="n">
-        <v>36363206.15177908</v>
+        <v>487973123.8755436</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3488,8 +3488,125 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRUMPUSDT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OFFICIAL TRUMP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENTER</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>entry_chased</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.273047884957256</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19.85770260282127</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.27297287801107</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.511095769914513</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.749143654871769</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.987191539829025</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.02547446185200188</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>164183.42539</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>170707.86868</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.678425</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.837018</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>914794088.206045</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG1"/>
+  <autoFilter ref="A1:AG2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3707,7 +3824,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -3726,7 +3843,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3770,14 +3887,14 @@
         <v>0.02640959622869432</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02638</v>
+        <v>0.02627</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1120661915389953</v>
+        <v>-0.5285814576091452</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -3802,22 +3919,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03791469194312642</v>
+        <v>0.03807348181992409</v>
       </c>
       <c r="AA2" t="n">
-        <v>22533.0120156</v>
+        <v>18322.4211032</v>
       </c>
       <c r="AB2" t="n">
-        <v>12251.9781237</v>
+        <v>12639.2128192</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.498956</v>
+        <v>19.306984</v>
       </c>
       <c r="AD2" t="n">
-        <v>254.069237</v>
+        <v>268.701897</v>
       </c>
       <c r="AE2" t="n">
-        <v>237286526.8349056</v>
+        <v>247839478.1186036</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3828,7 +3945,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -3891,10 +4008,10 @@
         <v>0.001010902989841661</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001141</v>
+        <v>0.0010654</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.86938622851592</v>
+        <v>5.390923828098915</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -3923,22 +4040,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.192796424502668</v>
+        <v>0.1220027215991822</v>
       </c>
       <c r="AA3" t="n">
-        <v>9881.433054928</v>
+        <v>13261.894231097</v>
       </c>
       <c r="AB3" t="n">
-        <v>8495.584516289</v>
+        <v>10692.633935367</v>
       </c>
       <c r="AC3" t="n">
-        <v>37.834685</v>
+        <v>32.077029</v>
       </c>
       <c r="AD3" t="n">
-        <v>369.950816</v>
+        <v>239.3828</v>
       </c>
       <c r="AE3" t="n">
-        <v>79003732.82059467</v>
+        <v>73545218.39797568</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -3949,7 +4066,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -4012,10 +4129,10 @@
         <v>0.0881281822103617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09217</v>
+        <v>0.09132999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.58629429118429</v>
+        <v>3.633137220504068</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4044,22 +4161,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1086130118388063</v>
+        <v>0.09852756034812288</v>
       </c>
       <c r="AA4" t="n">
-        <v>58469.0676636</v>
+        <v>109303.3702501</v>
       </c>
       <c r="AB4" t="n">
-        <v>54732.5031165</v>
+        <v>96946.0068477</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.451381</v>
+        <v>7.98636</v>
       </c>
       <c r="AD4" t="n">
-        <v>30.931245</v>
+        <v>16.734708</v>
       </c>
       <c r="AE4" t="n">
-        <v>821498659.5548553</v>
+        <v>812687003.9166681</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -4070,16 +4187,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>RIVERUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>River</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4126,13 +4243,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008539124282940763</v>
+        <v>18.5016932800241</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01074</v>
+        <v>22.2385</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.774021364885</v>
+        <v>20.19710662921026</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4140,19 +4257,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.007486231252880395</v>
+        <v>16.69515717614323</v>
       </c>
       <c r="T5" t="n">
-        <v>12.33022257520962</v>
+        <v>9.764166320016539</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009592017313001132</v>
+        <v>20.30822938390498</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0106449103430615</v>
+        <v>22.11476548778586</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01169780337312187</v>
+        <v>23.92130159166673</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -4161,22 +4278,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03074443455860293</v>
+        <v>0.0004496696052724645</v>
       </c>
       <c r="AA5" t="n">
-        <v>9597.195318724</v>
+        <v>13416.161101</v>
       </c>
       <c r="AB5" t="n">
-        <v>17536.443041871</v>
+        <v>10316.136733</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.126211</v>
+        <v>29.541366</v>
       </c>
       <c r="AD5" t="n">
-        <v>82.92800800000001</v>
+        <v>96.152759</v>
       </c>
       <c r="AE5" t="n">
-        <v>107477184.4761735</v>
+        <v>434502754.9490408</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -4187,16 +4304,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>MELANIAUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Official Melania Meme</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4206,24 +4323,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.2</v>
+        <v>60.344</v>
       </c>
       <c r="I6" t="n">
-        <v>68</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -4243,13 +4360,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>18.16763992150123</v>
+        <v>0.1112803252979652</v>
       </c>
       <c r="P6" t="n">
-        <v>21.814</v>
+        <v>0.11982</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.07063159691609</v>
+        <v>7.674020253956781</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4257,19 +4374,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>16.49196841873954</v>
+        <v>0.10264</v>
       </c>
       <c r="T6" t="n">
-        <v>9.223385701180424</v>
+        <v>7.764468044849582</v>
       </c>
       <c r="U6" t="n">
-        <v>19.84331142426293</v>
+        <v>0.1199206505959303</v>
       </c>
       <c r="V6" t="n">
-        <v>21.51898292702462</v>
+        <v>0.1285609758938955</v>
       </c>
       <c r="W6" t="n">
-        <v>23.19465442978631</v>
+        <v>0.1372013011918607</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -4278,33 +4395,37 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1452886923098024</v>
+        <v>0.4835751208937779</v>
       </c>
       <c r="AA6" t="n">
-        <v>12996.092697</v>
+        <v>3415.4931188</v>
       </c>
       <c r="AB6" t="n">
-        <v>9155.83409</v>
+        <v>4401.2964646</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.281283</v>
+        <v>78.270025</v>
       </c>
       <c r="AD6" t="n">
-        <v>107.994066</v>
+        <v>2315.714486</v>
       </c>
       <c r="AE6" t="n">
-        <v>425424556.8357913</v>
+        <v>119887969.8846735</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4323,7 +4444,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>btc_regime_caution | entry_chased</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4337,10 +4458,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>61.2</v>
+        <v>58.32</v>
       </c>
       <c r="I7" t="n">
-        <v>68</v>
+        <v>64.8</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -4360,13 +4481,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>219.1247632833021</v>
+        <v>220.6024049341364</v>
       </c>
       <c r="P7" t="n">
-        <v>237.53</v>
+        <v>235.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.39943256112139</v>
+        <v>6.916332154411009</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4374,19 +4495,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>204.2569217840868</v>
+        <v>205.4514637276878</v>
       </c>
       <c r="T7" t="n">
-        <v>6.78510327926425</v>
+        <v>6.867985510390086</v>
       </c>
       <c r="U7" t="n">
-        <v>233.9926047825175</v>
+        <v>235.7533461405849</v>
       </c>
       <c r="V7" t="n">
-        <v>248.8604462817329</v>
+        <v>250.9042873470335</v>
       </c>
       <c r="W7" t="n">
-        <v>263.7282877809482</v>
+        <v>266.055228553482</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -4395,22 +4516,22 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05898462186643622</v>
+        <v>0.03814286622449341</v>
       </c>
       <c r="AA7" t="n">
-        <v>226657.46683</v>
+        <v>341577.48471</v>
       </c>
       <c r="AB7" t="n">
-        <v>203045.18005</v>
+        <v>218731.28955</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.694521</v>
+        <v>4.779214</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.198316</v>
+        <v>6.364134</v>
       </c>
       <c r="AE7" t="n">
-        <v>2551194347.267691</v>
+        <v>2541602397.988404</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -4421,16 +4542,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MELANIAUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Official Melania Meme</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4445,19 +4566,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60.344</v>
+        <v>55.44</v>
       </c>
       <c r="I8" t="n">
-        <v>75.43000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -4477,13 +4598,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1112803252979652</v>
+        <v>0.008738855304062911</v>
       </c>
       <c r="P8" t="n">
-        <v>0.12347</v>
+        <v>0.0107432</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.95402504386616</v>
+        <v>22.93600965111779</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4491,54 +4612,50 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.10264</v>
+        <v>0.007609798769052171</v>
       </c>
       <c r="T8" t="n">
-        <v>7.764468044849582</v>
+        <v>12.91995914483002</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1199206505959303</v>
+        <v>0.009867911839073651</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1285609758938955</v>
+        <v>0.01099696837408439</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1372013011918607</v>
+        <v>0.01212602490909513</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3883180972413302</v>
+        <v>0.03259922972677217</v>
       </c>
       <c r="AA8" t="n">
-        <v>2868.5310179</v>
+        <v>8507.247731256</v>
       </c>
       <c r="AB8" t="n">
-        <v>4581.8561025</v>
+        <v>7925.514306041</v>
       </c>
       <c r="AC8" t="n">
-        <v>65.49919800000001</v>
+        <v>27.004767</v>
       </c>
       <c r="AD8" t="n">
-        <v>2669.233357</v>
+        <v>93.960216</v>
       </c>
       <c r="AE8" t="n">
-        <v>123955104.8551496</v>
+        <v>107747011.2370479</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG8"/>
